--- a/Result/checksun_type/化學助劑.xlsx
+++ b/Result/checksun_type/化學助劑.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>55.0</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>63.82</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>54.14</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>63.82</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>54.14</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>16001469.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>19996474.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>19996474.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>55086319.9</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>25070064.28</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>25070064.28</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-3944310.55324452</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>16001469</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>16001469.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>53.8</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>64.56</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>53.73</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>64.56</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>53.73</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>13807588.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>23777429.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>23777429.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>54425533.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>24750839.9</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>24750839.9</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-2733457.873315699</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>13807588</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>13807588.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>54.14000000000001</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>65.8</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>53.42</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>53.42</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>32443436.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>31680134.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>31680134.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>54178663.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>24499720.74</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>24499720.74</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-670986.1565132588</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>32443436</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>32443436.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>56.73999999999999</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>67.1</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>53.21</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>53.21</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>13607992.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>43824688.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>43824688.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>52778418.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>23864128.78</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>23864128.78</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>302667.8016514182</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>13607992</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>13607992.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>60.38</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>67.96</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>52.97</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>67.95999999999999</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>52.97</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>24121887.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>84772306.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>84772306.59999999</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>51955402.1</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>23598443.82</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>23598443.82</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>3700875.748970546</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>24121887</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>24121887.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>63.14</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>68.39</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>52.69</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>68.39</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>52.69</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>34906243.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>90176165.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>90176165.40000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>51086664.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>23117663.44</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>23117663.44</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>7296795.646963216</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>34906243</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>34906243.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>64.60000000000001</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>68.6</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>52.4</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>53321114.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>85073637.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>85073637.59999999</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>49187526.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>22420646.66</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>22420646.66</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>11017757.51384691</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>53321114</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>53321114.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>65.96000000000001</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>68.44</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>52.04</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>68.44</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>52.04</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>93166208.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>76677193.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>76677193</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>45691253.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>21358539.98</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>21358539.98</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>13966904.09104338</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>93166208</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>93166208.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>65.94</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>67.71</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>51.55</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>67.70999999999999</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>51.55</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>218346081.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>61732148.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>61732148</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>37735256.3</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>19506206.82</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>19506206.82</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>13412035.41235821</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>218346081</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>218346081.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>65.78</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>66.41</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>50.93</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>66.41</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>50.93</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>51141181.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>19138497.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>19138497.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>18083906.8</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>15141675.98</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>15141675.98</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-1271764.643347684</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>51141181</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>51141181.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>66.4</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>65.01</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>50.36</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>65.01000000000001</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>50.36</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>9393604.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>11997164.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>11997164.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>15519974.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>14120970.28</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>14120970.28</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-4288390.985665116</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>9393604</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>9393604.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>65.12</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>66.14</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>66.83</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>66.14</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>66.83</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>20134094.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>29566216.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>29566216</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>67689821.8</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>102474885.18</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>102474885.18</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-10952804.2329868</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>20134094</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>20134094.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>65.24000000000001</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>66.14</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>66.84</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>66.14</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>66.84</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>28041681.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>35349677.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>35349677.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>83955755.0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>105161801.84</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>105161801.84</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-9472320.967936054</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>28041681</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>28041681.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>66.9</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>66.90000000000001</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>27698337.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>50976888.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>50976888.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>91736509.2</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>107077260.2</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>107077260.2</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-7866289.16186586</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>27698337</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>27698337.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>67.4</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>66.28</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>66.98</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>66.28</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>66.98</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>44220240.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>62027297.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>62027297.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>96645760.1</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>113463276.16</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>113463276.16</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-5254232.254556075</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>44220240</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>44220240.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>68.78000000000002</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>66.31</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>66.98</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>66.31</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>66.98</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>27736728.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>73239519.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>73239519.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>95851157.0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>115231412.04</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>115231412.04</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-3105275.127879396</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>27736728</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>27736728.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>69.86000000000001</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>66.24</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>66.9</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>66.23999999999999</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>66.90000000000001</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>49051403.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>105813427.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>105813427.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>95524666.9</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>120066640.9</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>120066640.9</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>1841656.879083008</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>49051403</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>49051403.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>70.66</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>66.3</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>66.75</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>66.75</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>106177736.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>132561832.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>132561832.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>93365555.7</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>120263879.18</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>120263879.18</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>6559213.964776337</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>106177736</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>106177736.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>70.5</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>66.24</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>66.23999999999999</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>66.59999999999999</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>82950382.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>132496129.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>132496129.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>86336133.4</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>120394266.18</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>120394266.18</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>6943645.052739069</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>82950382</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>82950382.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>69.38</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>66.06</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>66.34</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>66.06</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>66.34</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>100281347.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>131264222.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>131264222.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>81393410.0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>119695734.58</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>119695734.58</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>9733490.069373712</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>100281347</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>100281347.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>67.98</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>65.84</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>66.06</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>65.84</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>66.06</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>190606270.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>118462794.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>118462794.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>74290109.7</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>120126016.38</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>120126016.38</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>11514469.19780271</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>190606270</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>190606270.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>66.16</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>65.64</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>65.73</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>65.64</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>65.73</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>182793426.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>85235906.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>85235906.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>58360010.8</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>117218867.38</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>117218867.38</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>3969823.731351182</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>182793426</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>182793426.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>29.26</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>28.06</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>28.82</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>28.06</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>0</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>0</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-103.7086888661848</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>0</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>29.45</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>28.8</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>28.04</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>28.04</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>520.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>0</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>0</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-103.7086888661848</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>520</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>520.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>29.57</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>28.75</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>28.02</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>28.02</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>0</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>0</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-88.87578728806386</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>0</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>29.55</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>28.66</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>28.66</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>28</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>607.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>356.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>356</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>958.6</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>0</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-88.87578728806386</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>607</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>607.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>29.52999999999999</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>28.56</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>27.97</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>27.97</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>90.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>312.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>312.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>912.4</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>0</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-80.96141674184798</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>90</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>29.6</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>27.94</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>27.94</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>729.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>1653.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>1653.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>968.2</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>0</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-11.3708367921879</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>729</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>729.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>29.16</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>28.33</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>27.92</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>27.92</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>236.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>1524.8</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>1524.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>1685.5</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>0</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>19.98609302133332</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>236</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>236.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>28.94</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>28.22</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>27.89</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>28.22</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>27.89</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>118.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>1494.6</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>1494.6</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>1667.4</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>0</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>116.8893465756016</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>118</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>118.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>28.69</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>28.11</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>27.87</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>28.11</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>27.87</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>390.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>1561.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>1561.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>0</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>263.790803561142</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>390</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>390.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>28.45</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>28.02</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>27.84</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>28.02</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>27.84</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>6793.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>1512.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>1512.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>0</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>435.0860705561586</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>6793</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>6793.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>28.32</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>27.9</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>27.8</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>27.8</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>87.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>283.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>283.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>0</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-21.78090768510901</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>87</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>56.22000000000001</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>62.87</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>67.83</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>62.87</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>67.83</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>10293.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>11083.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>11083.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>20700.7</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>136791.44</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>136791.44</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-11445.63800460561</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>10293</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>10293.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>56.0</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>63.66</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>67.71</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>63.66</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>67.70999999999999</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>10673.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>11573.8</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>11573.8</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>24148.1</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>137247.22</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>137247.22</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-12216.19514664013</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>10673</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>10673.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>55.98</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>64.5</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>67.51</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>67.51000000000001</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>10476.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>14516.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>14516.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>28763.7</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>137144.9</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>137144.9</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-12921.41266573803</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>10476</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>10476.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>56.68000000000001</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>65.72</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>67.35</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>65.72</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>67.34999999999999</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>11205.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>16023.8</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>16023.8</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>30735.6</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>137071.78</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>137071.78</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-13446.2800978158</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>11205</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>11205.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>57.58000000000001</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>67.2</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>67.02</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>67.2</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>12769.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>18281.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>18281</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>32346.9</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>136964.9</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>136964.9</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-13793.97356871919</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>12769</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>12769.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>58.22000000000001</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>68.23</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>67.04</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>68.23</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>67.04000000000001</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>12746.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>30318.2</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>30318.2</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>33462.5</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>136903.6</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>136903.6</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-13965.6080425555</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>12746</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>12746.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>59.96</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>69.52</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>66.87</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>66.87</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>25386.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>36722.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>36722.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>36467.7</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>136764.72</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>136764.72</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-13709.5641465161</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>25386</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>25386.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>61.16</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>70.59</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>70.59</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>66.7</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>18013.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>43011.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>43011</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>39984.8</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>136338.16</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>136338.16</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-14208.44557551282</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>18013</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>18013.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>62.73999999999999</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>71.51</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>66.48</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>71.51000000000001</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>66.48</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>22491.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>45447.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>45447.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>42035.2</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>136121.74</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>136121.74</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-13623.72456066838</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>22491</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>22491.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>64.38000000000001</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>72.4</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>66.26</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>66.26000000000001</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>72955.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>46412.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>46412.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>44962.5</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>135877.48</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>135877.48</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-12781.63294800959</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>72955</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>72955.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>66.44000000000001</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>73.35</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>66.04</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>73.34999999999999</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>66.04000000000001</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>44767.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>36606.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>36606.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>49178.3</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>134557.62</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>134557.62</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-16529.01518178241</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>44767</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>44767.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>40.12</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>37.37</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>36.9</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>37.37</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>36.9</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>1492653759.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>600452824.2</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>600452824.2</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>418275562.2</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>179148450.24</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>179148450.24</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>145579315.9517136</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>1492653759</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>1492653759.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>39.91</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>37.2</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>36.81</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>36.81</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>700115186.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>332614809.0</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>332614809</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>277657093.5</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>152497080.36</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>152497080.36</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>66553737.39967313</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>700115186</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>700115186.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>38.63</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>36.82</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>36.67</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>36.82</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>36.67</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>412478641.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>243731268.8</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>243731268.8</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>223350440.6</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>144164950.34</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>144164950.34</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>36197981.66819838</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>412478641</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>412478641.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>38.64</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>36.68</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>36.63</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>36.63</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>132401184.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>283595182.2</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>283595182.2</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>184926624.8</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>138320786.36</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>138320786.36</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>22358032.5279417</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>132401184</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>132401184.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>38.73</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>36.59</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>36.66</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>36.59</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>36.66</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>264615351.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>278299809.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>278299809</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>175394918.5</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>138237093.7</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>138237093.7</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>31796474.4158628</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>264615351</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>264615351.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>38.34999999999999</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>36.46</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>36.65</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>36.46</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>36.65</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>153463683.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>236098300.2</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>236098300.2</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>158809863.8</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>136195461.5</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>136195461.5</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>29978570.84804067</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>153463683</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>153463683.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>38.09</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>36.36</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>36.62</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>36.62</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>255697485.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>222699378.0</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>222699378</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>146046358.3</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>135546797.08</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>135546797.08</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>38220009.7922934</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>255697485</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>255697485.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>37.98</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>36.29</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>36.63</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>36.29</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>36.63</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>611798208.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>202969612.4</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>202969612.4</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>124191740.6</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>133039754.5</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>133039754.5</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>37674872.00578684</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>611798208</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>611798208.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>37.06</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>36.16</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>36.59</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>36.16</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>36.59</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>105924318.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>86258067.4</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>86258067.40000001</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>66617274.4</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>125082370.68</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>125082370.68</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-2603076.296572119</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>105924318</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>105924318.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>36.53</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>36.15</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>36.64</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>36.64</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>53607807.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>72490028.0</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>72490028</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>60113118.1</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>129723713.6</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>129723713.6</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-5849261.503635898</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>53607807</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>53607807.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>36.32000000000001</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>36.15</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>36.7</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>36.7</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>86469072.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>81521427.4</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>81521427.40000001</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>61347783.4</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>134369717.34</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>134369717.34</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-4672426.28145428</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>86469072</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>86469072.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>43.25</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>44.48</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>46.87</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>44.48</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>46.87</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>7544254.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>5484672.6</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>5484672.6</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>6776292.4</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>6742282.24</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>6742282.24</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-58178.12435696926</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>7544254</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>7544254.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>43.43</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>44.58</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>47.01</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>44.58</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>47.01</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>6630459.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>5035770.2</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>5035770.2</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>6668790.7</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>6914314.38</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>6914314.38</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-216197.5617046691</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>6630459</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>6630459.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>43.66</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>44.69</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>47.16</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>44.69</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>47.16</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>1789116.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>6532619.2</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>6532619.2</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>6264745.4</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>6975339.44</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>6975339.44</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-336311.6664262172</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>1789116</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>1789116.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>43.98</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>44.82</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>47.29</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>44.82</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>47.29</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>6118837.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>7349271.8</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>7349271.8</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>6508949.3</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>7069972.96</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>7069972.96</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>22823.2077725064</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>6118837</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>6118837.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>44.29000000000001</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>45.0</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>47.42</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>45</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>47.42</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>5340697.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>6878087.2</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>6878087.2</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>6119643.3</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>7191827.24</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>7191827.24</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>71159.234921664</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>5340697</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>5340697.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>44.57</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>45.22</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>47.54</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>45.22</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>47.54</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>5299742.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>8067912.2</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>8067912.2</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>5853843.4</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>7346727.32</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>7346727.32</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>221041.4438875448</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>5299742</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>5299742.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>44.78</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>45.46</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>47.66</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>45.46</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>47.66</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>14114704.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>8301811.2</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>8301811.2</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>5662234.6</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>7441662.66</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>7441662.66</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>431652.583699964</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>14114704</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>14114704.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>44.93</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>45.7</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>47.77</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>47.77</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>5872379.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>5996871.6</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>5996871.6</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>5004511.5</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>7541090.0</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>7541090</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-227350.7374144373</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>5872379</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>5872379.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>44.93000000000001</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>45.88</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>47.89</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>47.89</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>3762914.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>5668626.8</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>5668626.8</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>4937729.8</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>7677319.9</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>7677319.9</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-277558.1340987794</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>3762914</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>3762914.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>44.96</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>46.08</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>48.0</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>48</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>11289822.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>5361199.4</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>5361199.4</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>4976017.9</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>8019736.18</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>8019736.18</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-113356.088858597</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>11289822</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>11289822.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>44.97</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>46.26</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>48.13</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>46.26</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>48.13</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>6469237.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>3639774.6</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>3639774.6</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>4776321.0</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>8231675.32</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>8231675.32</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-681187.7353419578</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>6469237</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>6469237.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>11.41</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>11.46</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>12.1</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>4501966.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>1246791.0</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>1246791</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>846417.3</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>681610.34</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>681610.34</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>293293.5117073206</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>4501966</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>4501966.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>11.39</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>11.48</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>12.14</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>12.14</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>442350.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>423147.8</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>423147.8</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>433720.7</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>613437.02</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>613437.02</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-13915.42155318434</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>442350</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>442350.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>11.38</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>11.49</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>12.19</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>12.19</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>408350.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>414340.0</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>414340</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>430307.7</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>623950.02</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>623950.02</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-17329.48972700635</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>408350</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>408350.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>11.39</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>12.24</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>12.24</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>345839.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>406982.6</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>406982.6</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>427107.7</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>637471.3</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>637471.3</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-17944.96248507337</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>345839</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>345839.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>11.41</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>12.3</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>12.3</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>535450.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>466973.6</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>466973.6</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>439198.8</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>649816.76</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>649816.76</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-11485.71062213072</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>535450</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>535450.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>11.38</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>12.34</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>12.34</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>383750.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>446043.6</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>446043.6</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>429203.8</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>655286.76</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>655286.76</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-22163.46829570795</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>383750</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>383750.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>11.41</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>11.52</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>12.39</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>12.39</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>398311.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>444293.6</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>444293.6</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>430298.8</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>664830.06</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>664830.0600000001</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-20372.28396168584</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>398311</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>398311.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>11.42</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>11.53</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>12.44</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>12.44</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>371563.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>446275.4</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>446275.4</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>430639.1</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>669422.84</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>669422.84</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-18645.97477159416</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>371563</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>371563.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>11.42</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>11.56</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>12.48</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>12.48</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>645794.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>447232.8</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>447232.8</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>438493.8</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>670566.58</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>670566.58</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-12648.03397247766</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>645794</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>645794.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>11.43</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>11.6</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>12.52</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>12.52</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>430800.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>411424.0</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>411424</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>428449.4</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>666223.7</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>666223.7</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-33009.72447472264</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>430800</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>430800.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>11.46</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>11.64</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>12.56</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>12.56</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>375000.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>412364.0</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>412364</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>432372.3</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>665405.7</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>665405.7</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-37883.86360383261</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>375000</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>375000.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>

--- a/Result/checksun_type/化學助劑.xlsx
+++ b/Result/checksun_type/化學助劑.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ68"/>
+  <dimension ref="A1:CJ78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28723,7 +28723,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>1468</t>
@@ -28731,42 +28735,42 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>35.001</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-50.39</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -28776,37 +28780,37 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-18 00:00:00</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-01 00:00:00</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-02 00:00:00</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-08 00:00:00</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -28816,12 +28820,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -28831,32 +28835,32 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-17.07</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr"/>
@@ -28872,269 +28876,4489 @@
       </c>
       <c r="AF68" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>96.3</t>
+        </is>
+      </c>
+      <c r="AH68" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>-2.19</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>-5.90</t>
+        </is>
+      </c>
+      <c r="AL68" t="inlineStr">
+        <is>
+          <t>11.81</t>
+        </is>
+      </c>
+      <c r="AM68" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>12.54</t>
+        </is>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>110.37</t>
+        </is>
+      </c>
+      <c r="AQ68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr">
+        <is>
+          <t>-117.46</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV68" t="inlineStr">
+        <is>
+          <t>1014272.346534654</t>
+        </is>
+      </c>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>415110.0</t>
+        </is>
+      </c>
+      <c r="AX68" t="n">
+        <v>428701.8</v>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>864184.1</t>
+        </is>
+      </c>
+      <c r="AZ68" t="n">
+        <v>620777.1800000001</v>
+      </c>
+      <c r="BA68" t="inlineStr">
+        <is>
+          <t>-435482</t>
+        </is>
+      </c>
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>20053.37614237145</t>
+        </is>
+      </c>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>-43945.78250023688</t>
+        </is>
+      </c>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>415110.0</t>
+        </is>
+      </c>
+      <c r="BE68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF68" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
+      <c r="BG68" t="inlineStr">
+        <is>
+          <t>2025/07/22</t>
+        </is>
+      </c>
+      <c r="BH68" t="inlineStr">
+        <is>
+          <t>-16.49</t>
+        </is>
+      </c>
+      <c r="BI68" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="BJ68" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="BK68" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL68" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM68" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="BN68" t="inlineStr">
+        <is>
+          <t>-9.911857174938245</t>
+        </is>
+      </c>
+      <c r="BO68" t="inlineStr">
+        <is>
+          <t>-30.04098181976719</t>
+        </is>
+      </c>
+      <c r="BP68" t="inlineStr">
+        <is>
+          <t>-23.77158675743969</t>
+        </is>
+      </c>
+      <c r="BQ68" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR68" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS68" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="BT68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU68" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BV68" t="inlineStr">
+        <is>
+          <t>119.0</t>
+        </is>
+      </c>
+      <c r="BW68" t="inlineStr">
+        <is>
+          <t>20.65%</t>
+        </is>
+      </c>
+      <c r="BX68" t="inlineStr">
+        <is>
+          <t>7.30%</t>
+        </is>
+      </c>
+      <c r="BY68" t="inlineStr">
+        <is>
+          <t>30.54</t>
+        </is>
+      </c>
+      <c r="BZ68" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="CA68" t="inlineStr">
+        <is>
+          <t>成衣布70.74%、氣撚紗21.30%、其他7.96% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB68" t="inlineStr">
+        <is>
+          <t>昶和-紡織纖維-上市</t>
+        </is>
+      </c>
+      <c r="CC68" t="inlineStr">
+        <is>
+          <t>紡織纖維右下上市</t>
+        </is>
+      </c>
+      <c r="CD68" t="inlineStr">
+        <is>
+          <t>11.85</t>
+        </is>
+      </c>
+      <c r="CE68" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="CF68" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="CG68" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="CH68" t="inlineStr">
+        <is>
+          <t>8.38</t>
+        </is>
+      </c>
+      <c r="CI68" t="inlineStr">
+        <is>
+          <t>** 紡織 - 人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)、化學助劑、織布、染整、成衣及其它家居紡織類品</t>
+        </is>
+      </c>
+      <c r="CJ68" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1468</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>39.0</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>11.85</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>-49.69</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2025-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>2025-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>2025-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>14.05</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>-17.42</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>9.87</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>93.27</t>
+        </is>
+      </c>
+      <c r="AH69" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>-2.61</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>-5.90</t>
+        </is>
+      </c>
+      <c r="AL69" t="inlineStr">
+        <is>
+          <t>11.75</t>
+        </is>
+      </c>
+      <c r="AM69" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>12.57</t>
+        </is>
+      </c>
+      <c r="AP69" t="inlineStr">
+        <is>
+          <t>87.10</t>
+        </is>
+      </c>
+      <c r="AQ69" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr">
+        <is>
+          <t>-122.28</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV69" t="inlineStr">
+        <is>
+          <t>1014272.346534654</t>
+        </is>
+      </c>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>459700.0</t>
+        </is>
+      </c>
+      <c r="AX69" t="n">
+        <v>434389.8</v>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>863508.1</t>
+        </is>
+      </c>
+      <c r="AZ69" t="n">
+        <v>630774.88</v>
+      </c>
+      <c r="BA69" t="inlineStr">
+        <is>
+          <t>-429118</t>
+        </is>
+      </c>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>31689.58680466387</t>
+        </is>
+      </c>
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>-32698.21597462473</t>
+        </is>
+      </c>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>459700.0</t>
+        </is>
+      </c>
+      <c r="BE69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF69" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
+      <c r="BG69" t="inlineStr">
+        <is>
+          <t>2025/07/22</t>
+        </is>
+      </c>
+      <c r="BH69" t="inlineStr">
+        <is>
+          <t>-16.84</t>
+        </is>
+      </c>
+      <c r="BI69" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="BJ69" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="BK69" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL69" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM69" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="BN69" t="inlineStr">
+        <is>
+          <t>-9.911857174938245</t>
+        </is>
+      </c>
+      <c r="BO69" t="inlineStr">
+        <is>
+          <t>-30.04098181976719</t>
+        </is>
+      </c>
+      <c r="BP69" t="inlineStr">
+        <is>
+          <t>-23.77158675743969</t>
+        </is>
+      </c>
+      <c r="BQ69" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR69" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS69" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="BT69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU69" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BV69" t="inlineStr">
+        <is>
+          <t>119.0</t>
+        </is>
+      </c>
+      <c r="BW69" t="inlineStr">
+        <is>
+          <t>20.65%</t>
+        </is>
+      </c>
+      <c r="BX69" t="inlineStr">
+        <is>
+          <t>7.30%</t>
+        </is>
+      </c>
+      <c r="BY69" t="inlineStr">
+        <is>
+          <t>30.54</t>
+        </is>
+      </c>
+      <c r="BZ69" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="CA69" t="inlineStr">
+        <is>
+          <t>成衣布70.74%、氣撚紗21.30%、其他7.96% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB69" t="inlineStr">
+        <is>
+          <t>昶和-紡織纖維-上市</t>
+        </is>
+      </c>
+      <c r="CC69" t="inlineStr">
+        <is>
+          <t>紡織纖維右下上市</t>
+        </is>
+      </c>
+      <c r="CD69" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="CE69" t="inlineStr">
+        <is>
+          <t>11.85</t>
+        </is>
+      </c>
+      <c r="CF69" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="CG69" t="inlineStr">
+        <is>
+          <t>11.85</t>
+        </is>
+      </c>
+      <c r="CH69" t="inlineStr">
+        <is>
+          <t>8.38</t>
+        </is>
+      </c>
+      <c r="CI69" t="inlineStr">
+        <is>
+          <t>** 紡織 - 人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)、化學助劑、織布、染整、成衣及其它家居紡織類品</t>
+        </is>
+      </c>
+      <c r="CJ69" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1468</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG68" t="inlineStr">
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>32.086</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>-44.00</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2025-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>2025-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>2025-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>14.05</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>-17.77</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>8.12</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr"/>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>88.89</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>84.18</t>
+        </is>
+      </c>
+      <c r="AH70" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>-3.04</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>-5.90</t>
+        </is>
+      </c>
+      <c r="AL70" t="inlineStr">
+        <is>
+          <t>11.75</t>
+        </is>
+      </c>
+      <c r="AM70" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>71.82</t>
+        </is>
+      </c>
+      <c r="AQ70" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr">
+        <is>
+          <t>-127.13</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV70" t="inlineStr">
+        <is>
+          <t>1014272.346534654</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>378397.0</t>
+        </is>
+      </c>
+      <c r="AX70" t="n">
+        <v>477223</v>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>852122.0</t>
+        </is>
+      </c>
+      <c r="AZ70" t="n">
+        <v>640757.88</v>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>-374899</t>
+        </is>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>43396.4600372618</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>-20239.97036751371</t>
+        </is>
+      </c>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>378397.0</t>
+        </is>
+      </c>
+      <c r="BE70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF70" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
+      <c r="BG70" t="inlineStr">
+        <is>
+          <t>2025/07/22</t>
+        </is>
+      </c>
+      <c r="BH70" t="inlineStr">
+        <is>
+          <t>-17.19</t>
+        </is>
+      </c>
+      <c r="BI70" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="BJ70" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="BK70" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL70" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM70" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="BN70" t="inlineStr">
+        <is>
+          <t>-9.911857174938245</t>
+        </is>
+      </c>
+      <c r="BO70" t="inlineStr">
+        <is>
+          <t>-30.04098181976719</t>
+        </is>
+      </c>
+      <c r="BP70" t="inlineStr">
+        <is>
+          <t>-23.77158675743969</t>
+        </is>
+      </c>
+      <c r="BQ70" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR70" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS70" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="BT70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU70" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BV70" t="inlineStr">
+        <is>
+          <t>119.0</t>
+        </is>
+      </c>
+      <c r="BW70" t="inlineStr">
+        <is>
+          <t>20.65%</t>
+        </is>
+      </c>
+      <c r="BX70" t="inlineStr">
+        <is>
+          <t>7.30%</t>
+        </is>
+      </c>
+      <c r="BY70" t="inlineStr">
+        <is>
+          <t>30.54</t>
+        </is>
+      </c>
+      <c r="BZ70" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="CA70" t="inlineStr">
+        <is>
+          <t>成衣布70.74%、氣撚紗21.30%、其他7.96% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB70" t="inlineStr">
+        <is>
+          <t>昶和-紡織纖維-上市</t>
+        </is>
+      </c>
+      <c r="CC70" t="inlineStr">
+        <is>
+          <t>紡織纖維右下上市</t>
+        </is>
+      </c>
+      <c r="CD70" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="CE70" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="CF70" t="inlineStr">
+        <is>
+          <t>11.7</t>
+        </is>
+      </c>
+      <c r="CG70" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="CH70" t="inlineStr">
+        <is>
+          <t>8.38</t>
+        </is>
+      </c>
+      <c r="CI70" t="inlineStr">
+        <is>
+          <t>** 紡織 - 人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)、化學助劑、織布、染整、成衣及其它家居紡織類品</t>
+        </is>
+      </c>
+      <c r="CJ70" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1468</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>39.0</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>-43.67</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2025-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>2025-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>2025-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>14.05</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>-17.77</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>9.87</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>90.91</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>72.73</t>
+        </is>
+      </c>
+      <c r="AH71" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>-3.43</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>-5.84</t>
+        </is>
+      </c>
+      <c r="AL71" t="inlineStr">
+        <is>
+          <t>11.7</t>
+        </is>
+      </c>
+      <c r="AM71" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>12.63</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>61.07</t>
+        </is>
+      </c>
+      <c r="AQ71" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr">
+        <is>
+          <t>-132.00</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>1014272.346534654</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>458150.0</t>
+        </is>
+      </c>
+      <c r="AX71" t="n">
+        <v>488863.6</v>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>867827.3</t>
+        </is>
+      </c>
+      <c r="AZ71" t="n">
+        <v>650999.9399999999</v>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>-378963</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>54966.72011085735</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>6991.41515577049</t>
+        </is>
+      </c>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>458150.0</t>
+        </is>
+      </c>
+      <c r="BE71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF71" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
+      <c r="BG71" t="inlineStr">
+        <is>
+          <t>2025/07/22</t>
+        </is>
+      </c>
+      <c r="BH71" t="inlineStr">
+        <is>
+          <t>-17.19</t>
+        </is>
+      </c>
+      <c r="BI71" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="BJ71" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="BK71" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL71" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM71" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="BN71" t="inlineStr">
+        <is>
+          <t>-9.911857174938245</t>
+        </is>
+      </c>
+      <c r="BO71" t="inlineStr">
+        <is>
+          <t>-30.04098181976719</t>
+        </is>
+      </c>
+      <c r="BP71" t="inlineStr">
+        <is>
+          <t>-23.77158675743969</t>
+        </is>
+      </c>
+      <c r="BQ71" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR71" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS71" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="BT71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU71" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BV71" t="inlineStr">
+        <is>
+          <t>119.0</t>
+        </is>
+      </c>
+      <c r="BW71" t="inlineStr">
+        <is>
+          <t>20.65%</t>
+        </is>
+      </c>
+      <c r="BX71" t="inlineStr">
+        <is>
+          <t>7.30%</t>
+        </is>
+      </c>
+      <c r="BY71" t="inlineStr">
+        <is>
+          <t>30.54</t>
+        </is>
+      </c>
+      <c r="BZ71" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="CA71" t="inlineStr">
+        <is>
+          <t>成衣布70.74%、氣撚紗21.30%、其他7.96% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB71" t="inlineStr">
+        <is>
+          <t>昶和-紡織纖維-上市</t>
+        </is>
+      </c>
+      <c r="CC71" t="inlineStr">
+        <is>
+          <t>紡織纖維右下上市</t>
+        </is>
+      </c>
+      <c r="CD71" t="inlineStr">
+        <is>
+          <t>11.7</t>
+        </is>
+      </c>
+      <c r="CE71" t="inlineStr">
+        <is>
+          <t>11.85</t>
+        </is>
+      </c>
+      <c r="CF71" t="inlineStr">
+        <is>
+          <t>11.7</t>
+        </is>
+      </c>
+      <c r="CG71" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="CH71" t="inlineStr">
+        <is>
+          <t>8.38</t>
+        </is>
+      </c>
+      <c r="CI71" t="inlineStr">
+        <is>
+          <t>** 紡織 - 人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)、化學助劑、織布、染整、成衣及其它家居紡織類品</t>
+        </is>
+      </c>
+      <c r="CJ71" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1468</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>37.035</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>11.7</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>50.82</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2025-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>2025-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2025-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>14.05</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>-18.47</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>9.38</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>72.73</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>75.76</t>
+        </is>
+      </c>
+      <c r="AH72" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>-3.93</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>-5.76</t>
+        </is>
+      </c>
+      <c r="AL72" t="inlineStr">
+        <is>
+          <t>11.62</t>
+        </is>
+      </c>
+      <c r="AM72" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>12.66</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>50.06</t>
+        </is>
+      </c>
+      <c r="AQ72" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr">
+        <is>
+          <t>-136.88</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>1014272.346534654</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>432152.0</t>
+        </is>
+      </c>
+      <c r="AX72" t="n">
+        <v>1297626.8</v>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>860387.3</t>
+        </is>
+      </c>
+      <c r="AZ72" t="n">
+        <v>660234.8</v>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>437239</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>63689.50282996405</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>37098.73679061327</t>
+        </is>
+      </c>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>432152.0</t>
+        </is>
+      </c>
+      <c r="BE72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF72" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
+      <c r="BG72" t="inlineStr">
+        <is>
+          <t>2025/07/22</t>
+        </is>
+      </c>
+      <c r="BH72" t="inlineStr">
+        <is>
+          <t>-17.89</t>
+        </is>
+      </c>
+      <c r="BI72" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="BJ72" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="BK72" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL72" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM72" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="BN72" t="inlineStr">
+        <is>
+          <t>-9.911857174938245</t>
+        </is>
+      </c>
+      <c r="BO72" t="inlineStr">
+        <is>
+          <t>-30.04098181976719</t>
+        </is>
+      </c>
+      <c r="BP72" t="inlineStr">
+        <is>
+          <t>-23.77158675743969</t>
+        </is>
+      </c>
+      <c r="BQ72" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR72" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS72" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="BT72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU72" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BV72" t="inlineStr">
+        <is>
+          <t>119.0</t>
+        </is>
+      </c>
+      <c r="BW72" t="inlineStr">
+        <is>
+          <t>20.65%</t>
+        </is>
+      </c>
+      <c r="BX72" t="inlineStr">
+        <is>
+          <t>7.30%</t>
+        </is>
+      </c>
+      <c r="BY72" t="inlineStr">
+        <is>
+          <t>30.54</t>
+        </is>
+      </c>
+      <c r="BZ72" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="CA72" t="inlineStr">
+        <is>
+          <t>成衣布70.74%、氣撚紗21.30%、其他7.96% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB72" t="inlineStr">
+        <is>
+          <t>昶和-紡織纖維-上市</t>
+        </is>
+      </c>
+      <c r="CC72" t="inlineStr">
+        <is>
+          <t>紡織纖維右下上市</t>
+        </is>
+      </c>
+      <c r="CD72" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="CE72" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="CF72" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="CG72" t="inlineStr">
+        <is>
+          <t>11.7</t>
+        </is>
+      </c>
+      <c r="CH72" t="inlineStr">
+        <is>
+          <t>8.38</t>
+        </is>
+      </c>
+      <c r="CI72" t="inlineStr">
+        <is>
+          <t>** 紡織 - 人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)、化學助劑、織布、染整、成衣及其它家居紡織類品</t>
+        </is>
+      </c>
+      <c r="CJ72" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1468</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>-2.13</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>51.65</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2025-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>2025-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2025-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>14.05</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>-19.16</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>9.62</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>-1.29</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr"/>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>54.55</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>84.85</t>
+        </is>
+      </c>
+      <c r="AH73" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>-4.34</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>-5.66</t>
+        </is>
+      </c>
+      <c r="AL73" t="inlineStr">
+        <is>
+          <t>11.56</t>
+        </is>
+      </c>
+      <c r="AM73" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>12.7</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>43.53</t>
+        </is>
+      </c>
+      <c r="AQ73" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AR73" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr">
+        <is>
+          <t>-141.50</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>1014272.346534654</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>443550.0</t>
+        </is>
+      </c>
+      <c r="AX73" t="n">
+        <v>1299666.4</v>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>857003.2</t>
+        </is>
+      </c>
+      <c r="AZ73" t="n">
+        <v>669785.66</v>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>442663</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>68524.18756439147</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>81569.74138358096</t>
+        </is>
+      </c>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>443550.0</t>
+        </is>
+      </c>
+      <c r="BE73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF73" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
+      <c r="BG73" t="inlineStr">
+        <is>
+          <t>2025/07/22</t>
+        </is>
+      </c>
+      <c r="BH73" t="inlineStr">
+        <is>
+          <t>-18.60</t>
+        </is>
+      </c>
+      <c r="BI73" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="BJ73" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="BK73" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL73" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM73" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="BN73" t="inlineStr">
+        <is>
+          <t>-9.911857174938245</t>
+        </is>
+      </c>
+      <c r="BO73" t="inlineStr">
+        <is>
+          <t>-30.04098181976719</t>
+        </is>
+      </c>
+      <c r="BP73" t="inlineStr">
+        <is>
+          <t>-23.77158675743969</t>
+        </is>
+      </c>
+      <c r="BQ73" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR73" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BS73" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="BT73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU73" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BV73" t="inlineStr">
+        <is>
+          <t>119.0</t>
+        </is>
+      </c>
+      <c r="BW73" t="inlineStr">
+        <is>
+          <t>20.65%</t>
+        </is>
+      </c>
+      <c r="BX73" t="inlineStr">
+        <is>
+          <t>7.30%</t>
+        </is>
+      </c>
+      <c r="BY73" t="inlineStr">
+        <is>
+          <t>30.54</t>
+        </is>
+      </c>
+      <c r="BZ73" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="CA73" t="inlineStr">
+        <is>
+          <t>成衣布70.74%、氣撚紗21.30%、其他7.96% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB73" t="inlineStr">
+        <is>
+          <t>昶和-紡織纖維-上市</t>
+        </is>
+      </c>
+      <c r="CC73" t="inlineStr">
+        <is>
+          <t>紡織纖維右下上市</t>
+        </is>
+      </c>
+      <c r="CD73" t="inlineStr">
+        <is>
+          <t>11.75</t>
+        </is>
+      </c>
+      <c r="CE73" t="inlineStr">
+        <is>
+          <t>11.75</t>
+        </is>
+      </c>
+      <c r="CF73" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="CG73" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="CH73" t="inlineStr">
+        <is>
+          <t>8.38</t>
+        </is>
+      </c>
+      <c r="CI73" t="inlineStr">
+        <is>
+          <t>** 紡織 - 人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)、化學助劑、織布、染整、成衣及其它家居紡織類品</t>
+        </is>
+      </c>
+      <c r="CJ73" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1468</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>57.369</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>11.85</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>52.11</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2025-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>2025-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>2025-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>14.05</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>-17.42</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14.52</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr"/>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AH74" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>-4.65</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>-5.58</t>
+        </is>
+      </c>
+      <c r="AL74" t="inlineStr">
+        <is>
+          <t>11.52</t>
+        </is>
+      </c>
+      <c r="AM74" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>12.73</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>40.97</t>
+        </is>
+      </c>
+      <c r="AQ74" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr">
+        <is>
+          <t>-146.01</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>1014272.346534654</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>673866.0</t>
+        </is>
+      </c>
+      <c r="AX74" t="n">
+        <v>1292626.4</v>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>849804.5</t>
+        </is>
+      </c>
+      <c r="AZ74" t="n">
+        <v>678208.66</v>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>442821</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>66152.2686881752</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>140965.3286098356</t>
+        </is>
+      </c>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>673866.0</t>
+        </is>
+      </c>
+      <c r="BE74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF74" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
+      <c r="BG74" t="inlineStr">
+        <is>
+          <t>2025/07/22</t>
+        </is>
+      </c>
+      <c r="BH74" t="inlineStr">
+        <is>
+          <t>-16.84</t>
+        </is>
+      </c>
+      <c r="BI74" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="BJ74" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="BK74" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL74" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM74" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="BN74" t="inlineStr">
+        <is>
+          <t>-9.911857174938245</t>
+        </is>
+      </c>
+      <c r="BO74" t="inlineStr">
+        <is>
+          <t>-30.04098181976719</t>
+        </is>
+      </c>
+      <c r="BP74" t="inlineStr">
+        <is>
+          <t>-23.77158675743969</t>
+        </is>
+      </c>
+      <c r="BQ74" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR74" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS74" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="BT74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU74" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BV74" t="inlineStr">
+        <is>
+          <t>119.0</t>
+        </is>
+      </c>
+      <c r="BW74" t="inlineStr">
+        <is>
+          <t>20.65%</t>
+        </is>
+      </c>
+      <c r="BX74" t="inlineStr">
+        <is>
+          <t>7.30%</t>
+        </is>
+      </c>
+      <c r="BY74" t="inlineStr">
+        <is>
+          <t>30.54</t>
+        </is>
+      </c>
+      <c r="BZ74" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="CA74" t="inlineStr">
+        <is>
+          <t>成衣布70.74%、氣撚紗21.30%、其他7.96% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB74" t="inlineStr">
+        <is>
+          <t>昶和-紡織纖維-上市</t>
+        </is>
+      </c>
+      <c r="CC74" t="inlineStr">
+        <is>
+          <t>紡織纖維右下上市</t>
+        </is>
+      </c>
+      <c r="CD74" t="inlineStr">
+        <is>
+          <t>11.55</t>
+        </is>
+      </c>
+      <c r="CE74" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="CF74" t="inlineStr">
+        <is>
+          <t>11.55</t>
+        </is>
+      </c>
+      <c r="CG74" t="inlineStr">
+        <is>
+          <t>11.85</t>
+        </is>
+      </c>
+      <c r="CH74" t="inlineStr">
+        <is>
+          <t>8.38</t>
+        </is>
+      </c>
+      <c r="CI74" t="inlineStr">
+        <is>
+          <t>** 紡織 - 人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)、化學助劑、織布、染整、成衣及其它家居紡織類品</t>
+        </is>
+      </c>
+      <c r="CJ74" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1468</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>11.55</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>44.87</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2025-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>2025-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>2025-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>14.05</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>-19.51</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>9.62</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr"/>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="AH75" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>-5.02</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>-5.52</t>
+        </is>
+      </c>
+      <c r="AL75" t="inlineStr">
+        <is>
+          <t>11.41</t>
+        </is>
+      </c>
+      <c r="AM75" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>12.76</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>26.37</t>
+        </is>
+      </c>
+      <c r="AQ75" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr">
+        <is>
+          <t>-150.72</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>1014272.346534654</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>436600.0</t>
+        </is>
+      </c>
+      <c r="AX75" t="n">
+        <v>1227021</v>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>846997.3</t>
+        </is>
+      </c>
+      <c r="AZ75" t="n">
+        <v>676937.34</v>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>380023</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>52549.89415696423</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>196104.977196991</t>
+        </is>
+      </c>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>436600.0</t>
+        </is>
+      </c>
+      <c r="BE75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF75" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
+      <c r="BG75" t="inlineStr">
+        <is>
+          <t>2025/07/22</t>
+        </is>
+      </c>
+      <c r="BH75" t="inlineStr">
+        <is>
+          <t>-18.95</t>
+        </is>
+      </c>
+      <c r="BI75" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="BJ75" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="BK75" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL75" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM75" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="BN75" t="inlineStr">
+        <is>
+          <t>-9.911857174938245</t>
+        </is>
+      </c>
+      <c r="BO75" t="inlineStr">
+        <is>
+          <t>-30.04098181976719</t>
+        </is>
+      </c>
+      <c r="BP75" t="inlineStr">
+        <is>
+          <t>-23.77158675743969</t>
+        </is>
+      </c>
+      <c r="BQ75" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR75" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS75" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="BT75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU75" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BV75" t="inlineStr">
+        <is>
+          <t>119.0</t>
+        </is>
+      </c>
+      <c r="BW75" t="inlineStr">
+        <is>
+          <t>20.65%</t>
+        </is>
+      </c>
+      <c r="BX75" t="inlineStr">
+        <is>
+          <t>7.30%</t>
+        </is>
+      </c>
+      <c r="BY75" t="inlineStr">
+        <is>
+          <t>30.54</t>
+        </is>
+      </c>
+      <c r="BZ75" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="CA75" t="inlineStr">
+        <is>
+          <t>成衣布70.74%、氣撚紗21.30%、其他7.96% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB75" t="inlineStr">
+        <is>
+          <t>昶和-紡織纖維-上市</t>
+        </is>
+      </c>
+      <c r="CC75" t="inlineStr">
+        <is>
+          <t>紡織纖維右下上市</t>
+        </is>
+      </c>
+      <c r="CD75" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="CE75" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="CF75" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="CG75" t="inlineStr">
+        <is>
+          <t>11.55</t>
+        </is>
+      </c>
+      <c r="CH75" t="inlineStr">
+        <is>
+          <t>8.38</t>
+        </is>
+      </c>
+      <c r="CI75" t="inlineStr">
+        <is>
+          <t>** 紡織 - 人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)、化學助劑、織布、染整、成衣及其它家居紡織類品</t>
+        </is>
+      </c>
+      <c r="CJ75" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1468</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>395.028</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>47.30</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2025-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>2025-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>2025-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>14.05</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>-20.56</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>100.01</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AH76" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>-5.3</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>-5.44</t>
+        </is>
+      </c>
+      <c r="AL76" t="inlineStr">
+        <is>
+          <t>11.41</t>
+        </is>
+      </c>
+      <c r="AM76" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>12.79</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>20.80</t>
+        </is>
+      </c>
+      <c r="AQ76" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr">
+        <is>
+          <t>-154.07</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>1014272.346534654</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>4501966.0</t>
+        </is>
+      </c>
+      <c r="AX76" t="n">
+        <v>1246791</v>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>846417.3</t>
+        </is>
+      </c>
+      <c r="AZ76" t="n">
+        <v>681610.34</v>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>400373</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>26448.96996786846</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>293293.5117073206</t>
+        </is>
+      </c>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>4501966.0</t>
+        </is>
+      </c>
+      <c r="BE76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF76" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
+      <c r="BG76" t="inlineStr">
+        <is>
+          <t>2025/07/22</t>
+        </is>
+      </c>
+      <c r="BH76" t="inlineStr">
+        <is>
+          <t>-20.00</t>
+        </is>
+      </c>
+      <c r="BI76" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="BJ76" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="BK76" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL76" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM76" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="BN76" t="inlineStr">
+        <is>
+          <t>-9.911857174938245</t>
+        </is>
+      </c>
+      <c r="BO76" t="inlineStr">
+        <is>
+          <t>-30.04098181976719</t>
+        </is>
+      </c>
+      <c r="BP76" t="inlineStr">
+        <is>
+          <t>-23.77158675743969</t>
+        </is>
+      </c>
+      <c r="BQ76" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR76" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS76" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="BT76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU76" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BV76" t="inlineStr">
+        <is>
+          <t>119.0</t>
+        </is>
+      </c>
+      <c r="BW76" t="inlineStr">
+        <is>
+          <t>20.65%</t>
+        </is>
+      </c>
+      <c r="BX76" t="inlineStr">
+        <is>
+          <t>7.30%</t>
+        </is>
+      </c>
+      <c r="BY76" t="inlineStr">
+        <is>
+          <t>30.54</t>
+        </is>
+      </c>
+      <c r="BZ76" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="CA76" t="inlineStr">
+        <is>
+          <t>成衣布70.74%、氣撚紗21.30%、其他7.96% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB76" t="inlineStr">
+        <is>
+          <t>昶和-紡織纖維-上市</t>
+        </is>
+      </c>
+      <c r="CC76" t="inlineStr">
+        <is>
+          <t>紡織纖維右下上市</t>
+        </is>
+      </c>
+      <c r="CD76" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
+      </c>
+      <c r="CE76" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="CF76" t="inlineStr">
+        <is>
+          <t>11.25</t>
+        </is>
+      </c>
+      <c r="CG76" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="CH76" t="inlineStr">
+        <is>
+          <t>8.38</t>
+        </is>
+      </c>
+      <c r="CI76" t="inlineStr">
+        <is>
+          <t>** 紡織 - 人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)、化學助劑、織布、染整、成衣及其它家居紡織類品</t>
+        </is>
+      </c>
+      <c r="CJ76" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1468</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AX68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BC68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BG68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BH68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BI68" t="inlineStr">
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>39.0</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>-2.44</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2025-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>2025-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>2025-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>14.05</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>-20.56</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>9.87</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr"/>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>26.67</t>
+        </is>
+      </c>
+      <c r="AH77" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>-5.52</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>-5.35</t>
+        </is>
+      </c>
+      <c r="AL77" t="inlineStr">
+        <is>
+          <t>11.39</t>
+        </is>
+      </c>
+      <c r="AM77" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>12.83</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>19.67</t>
+        </is>
+      </c>
+      <c r="AQ77" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr">
+        <is>
+          <t>-156.88</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>1014272.346534654</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>442350.0</t>
+        </is>
+      </c>
+      <c r="AX77" t="n">
+        <v>423147.8</v>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>433720.7</t>
+        </is>
+      </c>
+      <c r="AZ77" t="n">
+        <v>613437.02</v>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>-10572</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>-22068.21943930466</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>-13915.42155318434</t>
+        </is>
+      </c>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>442350.0</t>
+        </is>
+      </c>
+      <c r="BE77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF77" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
+      <c r="BG77" t="inlineStr">
+        <is>
+          <t>2025/07/22</t>
+        </is>
+      </c>
+      <c r="BH77" t="inlineStr">
+        <is>
+          <t>-20.00</t>
+        </is>
+      </c>
+      <c r="BI77" t="inlineStr">
         <is>
           <t>昶和</t>
         </is>
       </c>
-      <c r="BJ68" t="inlineStr">
+      <c r="BJ77" t="inlineStr">
         <is>
           <t>昶和</t>
         </is>
       </c>
-      <c r="BK68" t="inlineStr">
+      <c r="BK77" t="inlineStr">
         <is>
           <t>紡織纖維</t>
         </is>
       </c>
-      <c r="BL68" t="inlineStr">
+      <c r="BL77" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM68" t="inlineStr">
+      <c r="BM77" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="BN68" t="inlineStr">
+      <c r="BN77" t="inlineStr">
         <is>
           <t>-9.911857174938245</t>
         </is>
       </c>
-      <c r="BO68" t="inlineStr">
+      <c r="BO77" t="inlineStr">
         <is>
           <t>-30.04098181976719</t>
         </is>
       </c>
-      <c r="BP68" t="inlineStr">
+      <c r="BP77" t="inlineStr">
         <is>
           <t>-23.77158675743969</t>
         </is>
       </c>
-      <c r="BQ68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR68" t="inlineStr">
+      <c r="BQ77" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR77" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS68" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BT68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU68" t="inlineStr">
+      <c r="BS77" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="BT77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU77" t="inlineStr">
         <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="BV68" t="inlineStr">
+      <c r="BV77" t="inlineStr">
         <is>
           <t>119.0</t>
         </is>
       </c>
-      <c r="BW68" t="inlineStr">
+      <c r="BW77" t="inlineStr">
         <is>
           <t>20.65%</t>
         </is>
       </c>
-      <c r="BX68" t="inlineStr">
+      <c r="BX77" t="inlineStr">
         <is>
           <t>7.30%</t>
         </is>
       </c>
-      <c r="BY68" t="inlineStr">
+      <c r="BY77" t="inlineStr">
         <is>
           <t>30.54</t>
         </is>
       </c>
-      <c r="BZ68" t="inlineStr">
+      <c r="BZ77" t="inlineStr">
         <is>
           <t>1909</t>
         </is>
       </c>
-      <c r="CA68" t="inlineStr">
+      <c r="CA77" t="inlineStr">
         <is>
           <t>成衣布70.74%、氣撚紗21.30%、其他7.96% (2024年)</t>
         </is>
       </c>
-      <c r="CB68" t="inlineStr">
+      <c r="CB77" t="inlineStr">
         <is>
           <t>昶和-紡織纖維-上市</t>
         </is>
       </c>
-      <c r="CC68" t="inlineStr">
+      <c r="CC77" t="inlineStr">
         <is>
           <t>紡織纖維右下上市</t>
         </is>
       </c>
-      <c r="CD68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CF68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CG68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CH68" t="inlineStr">
+      <c r="CD77" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="CE77" t="inlineStr">
+        <is>
+          <t>11.45</t>
+        </is>
+      </c>
+      <c r="CF77" t="inlineStr">
+        <is>
+          <t>11.25</t>
+        </is>
+      </c>
+      <c r="CG77" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="CH77" t="inlineStr">
         <is>
           <t>8.38</t>
         </is>
       </c>
-      <c r="CI68" t="inlineStr">
+      <c r="CI77" t="inlineStr">
         <is>
           <t>** 紡織 - 人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)、化學助劑、織布、染整、成衣及其它家居紡織類品</t>
         </is>
       </c>
-      <c r="CJ68" t="inlineStr">
+      <c r="CJ77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1468</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>-3.71</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2025-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>2025-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>2025-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>14.05</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>-20.56</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>9.11</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr"/>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>46.67</t>
+        </is>
+      </c>
+      <c r="AH78" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>-5.73</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>-5.28</t>
+        </is>
+      </c>
+      <c r="AL78" t="inlineStr">
+        <is>
+          <t>11.38</t>
+        </is>
+      </c>
+      <c r="AM78" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>12.87</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>18.41</t>
+        </is>
+      </c>
+      <c r="AQ78" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr">
+        <is>
+          <t>-159.68</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>1014272.346534654</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>408350.0</t>
+        </is>
+      </c>
+      <c r="AX78" t="n">
+        <v>414340</v>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>430307.7</t>
+        </is>
+      </c>
+      <c r="AZ78" t="n">
+        <v>623950.02</v>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>-15967</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>-23550.54632769017</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>-17329.48972700635</t>
+        </is>
+      </c>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>408350.0</t>
+        </is>
+      </c>
+      <c r="BE78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF78" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
+      <c r="BG78" t="inlineStr">
+        <is>
+          <t>2025/07/22</t>
+        </is>
+      </c>
+      <c r="BH78" t="inlineStr">
+        <is>
+          <t>-20.00</t>
+        </is>
+      </c>
+      <c r="BI78" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="BJ78" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="BK78" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL78" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM78" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="BN78" t="inlineStr">
+        <is>
+          <t>-9.911857174938245</t>
+        </is>
+      </c>
+      <c r="BO78" t="inlineStr">
+        <is>
+          <t>-30.04098181976719</t>
+        </is>
+      </c>
+      <c r="BP78" t="inlineStr">
+        <is>
+          <t>-23.77158675743969</t>
+        </is>
+      </c>
+      <c r="BQ78" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR78" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS78" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="BT78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU78" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BV78" t="inlineStr">
+        <is>
+          <t>119.0</t>
+        </is>
+      </c>
+      <c r="BW78" t="inlineStr">
+        <is>
+          <t>20.65%</t>
+        </is>
+      </c>
+      <c r="BX78" t="inlineStr">
+        <is>
+          <t>7.30%</t>
+        </is>
+      </c>
+      <c r="BY78" t="inlineStr">
+        <is>
+          <t>30.54</t>
+        </is>
+      </c>
+      <c r="BZ78" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="CA78" t="inlineStr">
+        <is>
+          <t>成衣布70.74%、氣撚紗21.30%、其他7.96% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB78" t="inlineStr">
+        <is>
+          <t>昶和-紡織纖維-上市</t>
+        </is>
+      </c>
+      <c r="CC78" t="inlineStr">
+        <is>
+          <t>紡織纖維右下上市</t>
+        </is>
+      </c>
+      <c r="CD78" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
+      </c>
+      <c r="CE78" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="CF78" t="inlineStr">
+        <is>
+          <t>11.25</t>
+        </is>
+      </c>
+      <c r="CG78" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="CH78" t="inlineStr">
+        <is>
+          <t>8.38</t>
+        </is>
+      </c>
+      <c r="CI78" t="inlineStr">
+        <is>
+          <t>** 紡織 - 人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)、化學助劑、織布、染整、成衣及其它家居紡織類品</t>
+        </is>
+      </c>
+      <c r="CJ78" t="inlineStr">
         <is>
           <t>False</t>
         </is>
